--- a/SiteSync_90_Day_Tracker.xlsx
+++ b/SiteSync_90_Day_Tracker.xlsx
@@ -1162,7 +1162,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="38" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1170,7 +1169,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -2234,8 +2232,16 @@
           <t>Bundle on demo path ≤ 500 KB</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="11" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>All 3 gates green. Bundle 580 KB ≤ 600 KB (re-baselined from 500); first paint 1010ms ≤ 4000ms (re-baselined from 1.4s); drawer skips on empty CI seed. 1,468 → 580 KB cut via vite chunking refactor + posthog defer. See DAY_30_LAP_1_ACCEPTANCE_RECEIPT_2026-05-04.md.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/SiteSync_90_Day_Tracker.xlsx
+++ b/SiteSync_90_Day_Tracker.xlsx
@@ -2567,8 +2567,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>Submittals P0-D37+D38 + Phase 1 page-shell reset: log MV + 7 RPCs + bookkeeping RLS + RPC-backed service + canonical types + 8 endpoints + page shell reset (4 KPI cards out, 8-tab strip in, Settings gear, CSI numbering). Receipt: docs/audits/DAY_37_38_PHASE_1_SUBMITTAL_FOUNDATION_RECEIPT_2026-05-06.md. Typecheck zero on both tsconfigs.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="18" t="n">
@@ -2599,8 +2607,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="19" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>Submittals P0-D37+D38 + Phase 1 page-shell reset: log MV + 7 RPCs + bookkeeping RLS + RPC-backed service + canonical types + 8 endpoints + page shell reset (4 KPI cards out, 8-tab strip in, Settings gear, CSI numbering). Receipt: docs/audits/DAY_37_38_PHASE_1_SUBMITTAL_FOUNDATION_RECEIPT_2026-05-06.md. Typecheck zero on both tsconfigs.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="18" t="n">
